--- a/data/trans_orig/P36BPD03_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD03_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de raciones de verdura u hortalizas que consume al día en 2023</t>
+          <t>Población según el número de raciones de verdura u hortalizas que consume al día en 2023 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11706</t>
+          <t>11480</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30110</t>
+          <t>28330</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3279</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13435</t>
+          <t>13215</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18048</t>
+          <t>17370</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38260</t>
+          <t>38038</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>115599</t>
+          <t>116505</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>157187</t>
+          <t>159366</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57019</t>
+          <t>55776</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>83761</t>
+          <t>83018</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>181362</t>
+          <t>180196</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>233878</t>
+          <t>232715</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,43%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>212267</t>
+          <t>213907</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>258722</t>
+          <t>258243</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>218817</t>
+          <t>222193</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>255426</t>
+          <t>256272</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>444661</t>
+          <t>444946</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>505214</t>
+          <t>504215</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>52,93%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>94482</t>
+          <t>95478</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>133018</t>
+          <t>131952</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>116505</t>
+          <t>117873</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>149331</t>
+          <t>149517</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>222200</t>
+          <t>222508</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>273646</t>
+          <t>274695</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,83%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12681</t>
+          <t>13371</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33225</t>
+          <t>32884</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6314</t>
+          <t>6036</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22296</t>
+          <t>21217</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>22455</t>
+          <t>22175</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>46790</t>
+          <t>45511</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>83304</t>
+          <t>83831</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>123264</t>
+          <t>124314</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>60552</t>
+          <t>61601</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>87808</t>
+          <t>88068</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>152854</t>
+          <t>151700</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>197764</t>
+          <t>198461</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,82%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>198211</t>
+          <t>198160</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>244006</t>
+          <t>244762</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>168708</t>
+          <t>169879</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>202485</t>
+          <t>202357</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>381432</t>
+          <t>381764</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>435061</t>
+          <t>435766</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>52,3%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>87752</t>
+          <t>90314</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>126712</t>
+          <t>128001</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>95371</t>
+          <t>95034</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>127062</t>
+          <t>123837</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>194841</t>
+          <t>191882</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>242067</t>
+          <t>244081</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,29%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5763</t>
+          <t>6283</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38040</t>
+          <t>39965</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4119</t>
+          <t>3980</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13734</t>
+          <t>13860</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10762</t>
+          <t>10976</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>47234</t>
+          <t>46476</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30330</t>
+          <t>38746</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>167359</t>
+          <t>171324</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17004</t>
+          <t>16767</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31941</t>
+          <t>31473</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>49858</t>
+          <t>54179</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>185336</t>
+          <t>187007</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,39%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>319096</t>
+          <t>312534</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>598155</t>
+          <t>579223</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>75314</t>
+          <t>75122</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>96419</t>
+          <t>96295</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>404136</t>
+          <t>401951</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>710867</t>
+          <t>700014</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>83,82%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32237</t>
+          <t>39226</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>153264</t>
+          <t>159667</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40859</t>
+          <t>40718</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>60212</t>
+          <t>59918</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>62725</t>
+          <t>64342</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>212068</t>
+          <t>210212</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,17%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>48067</t>
+          <t>48735</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>84018</t>
+          <t>82282</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19583</t>
+          <t>17712</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55110</t>
+          <t>54986</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>69620</t>
+          <t>70622</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>126547</t>
+          <t>127052</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>213573</t>
+          <t>214066</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>275426</t>
+          <t>275541</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>84824</t>
+          <t>86611</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>219357</t>
+          <t>217028</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>275617</t>
+          <t>275044</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>473653</t>
+          <t>470928</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,42%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>467774</t>
+          <t>471164</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>539651</t>
+          <t>541787</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>200983</t>
+          <t>195745</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>491857</t>
+          <t>488943</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>612762</t>
+          <t>608065</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1003404</t>
+          <t>1001041</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>49,79%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>191117</t>
+          <t>193581</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>250443</t>
+          <t>253462</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>227991</t>
+          <t>231142</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>669949</t>
+          <t>665666</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>440515</t>
+          <t>441269</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1048843</t>
+          <t>1029894</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>51,22%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>25269</t>
+          <t>24635</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>52616</t>
+          <t>53559</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>26705</t>
+          <t>27900</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>50453</t>
+          <t>51651</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>59259</t>
+          <t>55224</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>97138</t>
+          <t>94837</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>104792</t>
+          <t>106369</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>146303</t>
+          <t>146732</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>130780</t>
+          <t>131413</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>203584</t>
+          <t>203666</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>241019</t>
+          <t>242524</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>332347</t>
+          <t>332577</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,31%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>208584</t>
+          <t>209440</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>255610</t>
+          <t>254599</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>434876</t>
+          <t>437648</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>583302</t>
+          <t>575154</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>666586</t>
+          <t>663368</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>822968</t>
+          <t>826109</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,87%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>66242</t>
+          <t>64097</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>103618</t>
+          <t>102104</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>105787</t>
+          <t>105912</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>168006</t>
+          <t>167793</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>181702</t>
+          <t>184454</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>254260</t>
+          <t>255515</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,45%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13294</t>
+          <t>14156</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>47176</t>
+          <t>53380</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>29547</t>
+          <t>30518</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>59953</t>
+          <t>60083</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>49418</t>
+          <t>50908</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>95724</t>
+          <t>95240</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>32335</t>
+          <t>34543</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>76962</t>
+          <t>79012</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>128367</t>
+          <t>129509</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>172218</t>
+          <t>170133</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>174775</t>
+          <t>174109</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>237753</t>
+          <t>235520</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,53%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>86078</t>
+          <t>86792</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>138459</t>
+          <t>141062</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>433601</t>
+          <t>434861</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>485815</t>
+          <t>486049</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>531120</t>
+          <t>533696</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>604913</t>
+          <t>607602</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,71%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>29694</t>
+          <t>28144</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>76820</t>
+          <t>74336</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>93059</t>
+          <t>92571</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>130299</t>
+          <t>128649</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>132856</t>
+          <t>130879</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>193935</t>
+          <t>190259</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,01%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>145429</t>
+          <t>145668</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>223989</t>
+          <t>226045</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>115886</t>
+          <t>118005</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>172654</t>
+          <t>174031</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>284077</t>
+          <t>280103</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>384827</t>
+          <t>378868</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>611068</t>
+          <t>568088</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>839687</t>
+          <t>842129</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>536681</t>
+          <t>502238</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>717869</t>
+          <t>715622</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1209074</t>
+          <t>1227017</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1518884</t>
+          <t>1530830</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,04%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1612939</t>
+          <t>1610199</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2115220</t>
+          <t>2180132</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1451787</t>
+          <t>1521097</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1979129</t>
+          <t>1980292</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3326997</t>
+          <t>3292094</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3988055</t>
+          <t>3955877</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>56,95%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>512055</t>
+          <t>500336</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>740965</t>
+          <t>741238</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>761620</t>
+          <t>761369</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1529370</t>
+          <t>1471883</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1372189</t>
+          <t>1397547</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2130391</t>
+          <t>2203782</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>31,73%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD03_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD03_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19090</t>
+          <t>19729</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11480</t>
+          <t>12073</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28330</t>
+          <t>29818</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6898</t>
+          <t>9777</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3130</t>
+          <t>4631</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13215</t>
+          <t>19328</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>25988</t>
+          <t>29506</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17370</t>
+          <t>19767</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38038</t>
+          <t>43148</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>136546</t>
+          <t>141225</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>116505</t>
+          <t>120024</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>159366</t>
+          <t>161893</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,22 +873,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>69166</t>
+          <t>73745</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55776</t>
+          <t>60862</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>83018</t>
+          <t>88805</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>205712</t>
+          <t>214970</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>180196</t>
+          <t>190392</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>232715</t>
+          <t>244500</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>23,53%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>236021</t>
+          <t>259947</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>213907</t>
+          <t>234185</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>258243</t>
+          <t>283339</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>238450</t>
+          <t>255933</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>222193</t>
+          <t>238073</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>256272</t>
+          <t>276818</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>474471</t>
+          <t>515880</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>444946</t>
+          <t>483777</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>504215</t>
+          <t>547769</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>52,72%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>113555</t>
+          <t>129717</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>95478</t>
+          <t>108793</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>131952</t>
+          <t>155403</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>132953</t>
+          <t>148957</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>117873</t>
+          <t>132223</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>149517</t>
+          <t>166862</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>246508</t>
+          <t>278674</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>222508</t>
+          <t>252303</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>274695</t>
+          <t>309031</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>29,74%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20843</t>
+          <t>21009</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13371</t>
+          <t>12823</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32884</t>
+          <t>32769</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11550</t>
+          <t>11493</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6036</t>
+          <t>6315</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21217</t>
+          <t>20903</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>32393</t>
+          <t>32502</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>22175</t>
+          <t>21700</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>45511</t>
+          <t>46608</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>101409</t>
+          <t>101499</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>83831</t>
+          <t>84984</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>124314</t>
+          <t>122368</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>73829</t>
+          <t>76779</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>61601</t>
+          <t>63099</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88068</t>
+          <t>90381</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>175238</t>
+          <t>178278</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>151700</t>
+          <t>153886</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>198461</t>
+          <t>204437</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>22,6%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>221489</t>
+          <t>241485</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>198160</t>
+          <t>216844</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>244762</t>
+          <t>263288</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>186408</t>
+          <t>208829</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>169879</t>
+          <t>190198</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>202357</t>
+          <t>225810</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>407898</t>
+          <t>450315</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>381764</t>
+          <t>420316</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>435766</t>
+          <t>480292</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>53,09%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>107763</t>
+          <t>118498</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>90314</t>
+          <t>97816</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>128001</t>
+          <t>139167</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>109922</t>
+          <t>125067</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>95034</t>
+          <t>109834</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>123837</t>
+          <t>143268</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>217685</t>
+          <t>243565</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>191882</t>
+          <t>219390</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>244081</t>
+          <t>271678</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>30,03%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>451504</t>
+          <t>482491</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>451504</t>
+          <t>482491</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>451504</t>
+          <t>482491</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>381709</t>
+          <t>422168</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>381709</t>
+          <t>422168</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>381709</t>
+          <t>422168</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>833214</t>
+          <t>904659</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>833214</t>
+          <t>904659</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>833214</t>
+          <t>904659</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>21137</t>
+          <t>22652</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6283</t>
+          <t>14840</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>39965</t>
+          <t>34645</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>8176</t>
+          <t>8819</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3980</t>
+          <t>4689</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13860</t>
+          <t>15524</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>29313</t>
+          <t>31472</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10976</t>
+          <t>21274</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46476</t>
+          <t>44010</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>101384</t>
+          <t>107964</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>38746</t>
+          <t>89227</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>171324</t>
+          <t>128002</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23139</t>
+          <t>25031</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16767</t>
+          <t>18545</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31473</t>
+          <t>34813</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>124523</t>
+          <t>132995</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>54179</t>
+          <t>112518</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>187007</t>
+          <t>154055</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>23,37%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>451618</t>
+          <t>231014</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>312534</t>
+          <t>206856</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>579223</t>
+          <t>251334</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>85914</t>
+          <t>97526</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>75122</t>
+          <t>85945</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>96295</t>
+          <t>109065</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>537532</t>
+          <t>328540</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>401951</t>
+          <t>302360</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>700014</t>
+          <t>353289</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>53,6%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>94125</t>
+          <t>109982</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39226</t>
+          <t>92629</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>159667</t>
+          <t>131651</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>49682</t>
+          <t>56121</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40718</t>
+          <t>46816</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>59918</t>
+          <t>68657</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>143807</t>
+          <t>166103</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>64342</t>
+          <t>145513</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>210212</t>
+          <t>189964</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>28,82%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>63515</t>
+          <t>67114</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>48735</t>
+          <t>50802</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>82282</t>
+          <t>86674</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>38434</t>
+          <t>41120</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17712</t>
+          <t>30283</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>54986</t>
+          <t>53698</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>101949</t>
+          <t>108234</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>70622</t>
+          <t>90285</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>127052</t>
+          <t>130365</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>242876</t>
+          <t>254911</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>214066</t>
+          <t>226975</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>275541</t>
+          <t>287108</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>164840</t>
+          <t>180656</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>86611</t>
+          <t>160257</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>217028</t>
+          <t>202594</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>407715</t>
+          <t>435567</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>275044</t>
+          <t>400530</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>470928</t>
+          <t>473126</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>505312</t>
+          <t>553321</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>471164</t>
+          <t>512118</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>541787</t>
+          <t>590308</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>380763</t>
+          <t>423440</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>195745</t>
+          <t>396558</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>488943</t>
+          <t>448141</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>886074</t>
+          <t>976760</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>608065</t>
+          <t>932051</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001041</t>
+          <t>1019643</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>51,25%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>221404</t>
+          <t>253606</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>193581</t>
+          <t>219092</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>253462</t>
+          <t>283203</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>393492</t>
+          <t>215425</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>231142</t>
+          <t>194420</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>665666</t>
+          <t>239575</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>614896</t>
+          <t>469031</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>441269</t>
+          <t>431802</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1029894</t>
+          <t>507975</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>25,53%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1033106</t>
+          <t>1128952</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1033106</t>
+          <t>1128952</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1033106</t>
+          <t>1128952</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>977529</t>
+          <t>860640</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>977529</t>
+          <t>860640</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>977529</t>
+          <t>860640</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2010634</t>
+          <t>1989592</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2010634</t>
+          <t>1989592</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2010634</t>
+          <t>1989592</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>36354</t>
+          <t>39175</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>24635</t>
+          <t>27809</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>53559</t>
+          <t>56281</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>38154</t>
+          <t>40461</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>27900</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>51651</t>
+          <t>50859</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>74507</t>
+          <t>79635</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>55224</t>
+          <t>63652</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>94837</t>
+          <t>99389</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>124487</t>
+          <t>142133</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>106369</t>
+          <t>120681</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>146732</t>
+          <t>163581</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>173092</t>
+          <t>183260</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>131413</t>
+          <t>166094</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>203666</t>
+          <t>205180</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>297579</t>
+          <t>325392</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>242524</t>
+          <t>295885</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>332577</t>
+          <t>358497</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,67%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>231434</t>
+          <t>275788</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>209440</t>
+          <t>248359</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>254599</t>
+          <t>304306</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>485557</t>
+          <t>437699</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>437648</t>
+          <t>413066</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>575154</t>
+          <t>460500</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>716991</t>
+          <t>713487</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>663368</t>
+          <t>678009</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>826109</t>
+          <t>749516</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>53,68%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>81741</t>
+          <t>109787</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>64097</t>
+          <t>89972</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>102104</t>
+          <t>137886</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>143151</t>
+          <t>168011</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>105912</t>
+          <t>150373</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>167793</t>
+          <t>188476</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>224892</t>
+          <t>277798</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>184454</t>
+          <t>249506</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>255515</t>
+          <t>308549</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>22,1%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>839954</t>
+          <t>829430</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>839954</t>
+          <t>829430</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>839954</t>
+          <t>829430</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1313970</t>
+          <t>1396312</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1313970</t>
+          <t>1396312</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1313970</t>
+          <t>1396312</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>26998</t>
+          <t>24725</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14156</t>
+          <t>13218</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>53380</t>
+          <t>43739</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>41541</t>
+          <t>41178</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>30518</t>
+          <t>30013</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>60083</t>
+          <t>56651</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>68539</t>
+          <t>65903</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>50908</t>
+          <t>48514</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>95240</t>
+          <t>88036</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>52876</t>
+          <t>42037</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>34543</t>
+          <t>27591</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>79012</t>
+          <t>62935</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>149087</t>
+          <t>162531</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>129509</t>
+          <t>142632</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>170133</t>
+          <t>187961</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>201963</t>
+          <t>204568</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>174109</t>
+          <t>178279</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>235520</t>
+          <t>237894</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>22,02%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>112755</t>
+          <t>125056</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>86792</t>
+          <t>100300</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>141062</t>
+          <t>149777</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>459561</t>
+          <t>513790</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>434861</t>
+          <t>486366</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>486049</t>
+          <t>541393</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>572316</t>
+          <t>638846</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>533696</t>
+          <t>602707</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>607602</t>
+          <t>672550</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>62,25%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>47878</t>
+          <t>45409</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>28144</t>
+          <t>26445</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>74336</t>
+          <t>67882</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>110101</t>
+          <t>125625</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>92571</t>
+          <t>106959</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>128649</t>
+          <t>146602</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>157979</t>
+          <t>171034</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>130879</t>
+          <t>143232</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>190259</t>
+          <t>203057</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,8%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>760290</t>
+          <t>843123</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>760290</t>
+          <t>843123</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>760290</t>
+          <t>843123</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1000797</t>
+          <t>1080351</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1000797</t>
+          <t>1080351</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1000797</t>
+          <t>1080351</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>187937</t>
+          <t>194404</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>145668</t>
+          <t>165576</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>226045</t>
+          <t>231881</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>144752</t>
+          <t>152847</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>118005</t>
+          <t>130362</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>174031</t>
+          <t>176568</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>332690</t>
+          <t>347252</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>280103</t>
+          <t>310068</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>378868</t>
+          <t>385982</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>759578</t>
+          <t>789768</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>568088</t>
+          <t>734932</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>842129</t>
+          <t>846451</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>653153</t>
+          <t>702001</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>502238</t>
+          <t>660998</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>715622</t>
+          <t>751294</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>1412731</t>
+          <t>1491769</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1227017</t>
+          <t>1416984</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1530830</t>
+          <t>1561734</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,09%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1758629</t>
+          <t>1686612</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1610199</t>
+          <t>1627176</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2180132</t>
+          <t>1760884</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1836653</t>
+          <t>1937216</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1521097</t>
+          <t>1881386</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1980292</t>
+          <t>1989726</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>3595281</t>
+          <t>3623828</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3292094</t>
+          <t>3546550</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3955877</t>
+          <t>3708244</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>52,46%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>666466</t>
+          <t>766999</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>500336</t>
+          <t>713420</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>741238</t>
+          <t>828904</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>939301</t>
+          <t>839204</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>761369</t>
+          <t>794858</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1471883</t>
+          <t>882361</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>1605767</t>
+          <t>1606203</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1397547</t>
+          <t>1536649</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2203782</t>
+          <t>1679876</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>23,76%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3372610</t>
+          <t>3437783</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3372610</t>
+          <t>3437783</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3372610</t>
+          <t>3437783</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>3573860</t>
+          <t>3631268</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3573860</t>
+          <t>3631268</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3573860</t>
+          <t>3631268</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>6946469</t>
+          <t>7069051</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>6946469</t>
+          <t>7069051</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6946469</t>
+          <t>7069051</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
